--- a/data/Updated_Summary_Mechanical_Characterization.xlsx
+++ b/data/Updated_Summary_Mechanical_Characterization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://epflch-my.sharepoint.com/personal/mati_shah_epfl_ch/Documents/PHD/05_Blind_prediction_documents/02_Preliminary_mechanical_properties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="13_ncr:1_{02B15726-10F0-4C76-903C-607CEEEBC404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8F149FB6-C23E-45B0-AD6D-4ECE490D12B2}"/>
+  <xr:revisionPtr revIDLastSave="220" documentId="13_ncr:1_{02B15726-10F0-4C76-903C-607CEEEBC404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD50EF5D-15C8-4A33-AAD7-7BA00E343694}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -62,9 +62,6 @@
     <t xml:space="preserve">Young's Modulus </t>
   </si>
   <si>
-    <t>Mortar for Construction</t>
-  </si>
-  <si>
     <t>Limestone</t>
   </si>
   <si>
@@ -129,6 +126,9 @@
   </si>
   <si>
     <t>Brick Paver</t>
+  </si>
+  <si>
+    <t>Mortar for plaster</t>
   </si>
 </sst>
 </file>
@@ -712,27 +712,27 @@
         <v>2</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>3</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D2" s="3">
         <v>4.0599999999999996</v>
@@ -747,7 +747,7 @@
         <v>41</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -756,7 +756,7 @@
         <v>6</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D3" s="3">
         <v>1.06</v>
@@ -771,7 +771,7 @@
         <v>29</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -780,7 +780,7 @@
         <v>7</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="3">
         <v>318.81</v>
@@ -795,18 +795,18 @@
         <v>43</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" s="3">
         <v>5.12</v>
@@ -821,7 +821,7 @@
         <v>11</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -830,7 +830,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D6" s="3">
         <v>1.44</v>
@@ -845,7 +845,7 @@
         <v>14</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -854,7 +854,7 @@
         <v>7</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" s="3">
         <v>466.82</v>
@@ -869,18 +869,18 @@
         <v>24</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" s="3">
         <v>6.64</v>
@@ -895,7 +895,7 @@
         <v>14</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -904,7 +904,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D9" s="3">
         <v>1.76</v>
@@ -919,7 +919,7 @@
         <v>15</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -928,7 +928,7 @@
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" s="3">
         <v>417.13</v>
@@ -943,18 +943,18 @@
         <v>23</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="9" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D11" s="3">
         <v>1.52</v>
@@ -969,7 +969,7 @@
         <v>10</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -978,7 +978,7 @@
         <v>6</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D12" s="3">
         <v>0.67</v>
@@ -993,7 +993,7 @@
         <v>2</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -1002,7 +1002,7 @@
         <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D13" s="3">
         <v>157</v>
@@ -1017,18 +1017,18 @@
         <v>33</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D14" s="3">
         <v>116.1</v>
@@ -1043,7 +1043,7 @@
         <v>11</v>
       </c>
       <c r="H14" s="10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
@@ -1052,7 +1052,7 @@
         <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="3">
         <v>27</v>
@@ -1070,39 +1070,39 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D16" s="3">
         <v>164.26</v>
       </c>
       <c r="E16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H16" s="4" t="s">
         <v>27</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D17" s="3">
         <v>93.44</v>
@@ -1117,18 +1117,18 @@
         <v>19</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>5</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D18" s="4">
         <v>0.67</v>
@@ -1143,19 +1143,19 @@
         <v>23</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="B29" s="7" t="s">
         <v>24</v>
-      </c>
-      <c r="B29" s="7" t="s">
-        <v>25</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
